--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -1,63 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arcadiso365-my.sharepoint.com/personal/vijaykumar_mani_arcadis_com/Documents/IPL 2026 Predictions/Individual Predictions/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_63C152B9D3B0DD20D75B2811595ED87656CDDE7F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE3CB463-4FAE-4395-BD4F-DAB8ADB97573}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Match</t>
-  </si>
-  <si>
-    <t>Toss</t>
-  </si>
-  <si>
-    <t>Match Winner</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -72,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,25 +420,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Toss</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Match Winner</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>12-03-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RCB vs SRH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SRH</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10:30:30</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,33 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>10:30:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>12-03-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MI vs KKR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10:30:41</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -1,37 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arcadiso365-my.sharepoint.com/personal/vijaykumar_mani_arcadis_com/Documents/IPL 2026 Predictions/Individual Predictions/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_63C152B9D3B0DD20D75B2811595ED87656CDDE7F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE3CB463-4FAE-4395-BD4F-DAB8ADB97573}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>Toss</t>
+  </si>
+  <si>
+    <t>Match Winner</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +72,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,93 +396,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Match</t>
-        </is>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Toss</t>
-        </is>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Match Winner</t>
-        </is>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>12-03-2026</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>RCB vs SRH</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SRH</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RCB</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10:30:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>12-03-2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MI vs KKR</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>10:30:41</t>
-        </is>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -1,63 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arcadiso365-my.sharepoint.com/personal/vijaykumar_mani_arcadis_com/Documents/IPL 2026 Predictions/Individual Predictions/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_63C152B9D3B0DD20D75B2811595ED87656CDDE7F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE3CB463-4FAE-4395-BD4F-DAB8ADB97573}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Match</t>
-  </si>
-  <si>
-    <t>Toss</t>
-  </si>
-  <si>
-    <t>Match Winner</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -72,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,25 +420,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Toss</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Match Winner</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>28-03-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RCB vs SRH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>12:38:31</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,33 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>12:38:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>29-03-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MI vs KKR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>12:02:53</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,33 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>12:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30-03-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RR vs CSK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>14:37:04</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,6 +533,33 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>14:37:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PBKS vs GT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>16:54:35</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,33 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>16:54:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>01-04-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LSG vs DC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LSG</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>11:17:17</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,6 +587,33 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>11:17:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>02-04-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KKR vs SRH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SRH</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15:14:44</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,6 +617,33 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>03-04-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CSK vs PBKS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10:10:49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,6 +644,33 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>04-04-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DC vs MI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>13:51:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,6 +671,33 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>04-04-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GT vs RR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>13:53:08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -698,6 +698,33 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>05-04-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SRH vs LSG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LSG</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SRH</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>14:39:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -725,6 +725,33 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>05-04-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RCB vs CSK</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>14:39:55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -743,12 +743,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RCB</t>
+          <t>CSK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14:39:55</t>
+          <t>17:26:10</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,6 +752,33 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>06-04-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KKR vs PBKS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>18:32:22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,31 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Match</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Toss</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Match Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -776,6 +764,33 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>18:32:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>07-04-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RR vs MI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>14:35:51</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,33 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>08-04-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DC vs GT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>18:30:51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -812,12 +812,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18:30:51</t>
+          <t>18:31:02</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,6 +821,33 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>09-04-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KKR vs LSG</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LSG</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>12:19:53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,6 +848,33 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>10-04-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>RR vs RCB</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>18:26:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,6 +875,33 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>11-04-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PBKS vs SRH</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SRH</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>08:57:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,33 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>11-04-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CSK vs DC</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>08:57:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,6 +929,33 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>12-04-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LSG vs GT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LSG</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>10:01:18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,6 +956,33 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12-04-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MI vs RCB</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>10:01:25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,6 +983,33 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>13-04-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SRH vs RR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>12:28:18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1010,6 +1010,33 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>14-04-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CSK vs KKR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>18:07:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,33 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>15-04-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RCB vs LSG</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>18:43:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,6 +1064,33 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16-04-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MI vs PBKS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>18:29:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,6 +1091,33 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>17-04-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GT vs KKR</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>18:25:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -1104,17 +1104,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>KKR</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18:25:40</t>
+          <t>18:56:18</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,6 +1118,33 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>18-04-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RCB vs DC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>08:32:02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1145,6 +1145,33 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>18-04-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SRH vs CSK</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SRH</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>08:32:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1172,33 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>19-04-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>KKR vs RR</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>14:27:13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1199,6 +1199,33 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>19-04-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PBKS vs LSG</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>14:27:20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1226,6 +1226,33 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20-04-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GT vs MI</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>18:31:22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,33 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>21-04-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SRH vs DC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SRH</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>18:33:33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1280,6 +1280,33 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>22-04-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LSG vs RR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LSG</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LSG</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>18:23:28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1307,6 +1307,33 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>23-04-2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MI vs CSK</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>18:18:38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1334,6 +1334,33 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>24-04-2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>RCB vs GT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>18:23:33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1361,6 +1361,33 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>25-04-2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DC vs PBKS</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>14:22:51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,6 +1388,33 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>25-04-2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>RR vs SRH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>14:23:02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1415,6 +1415,33 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>26-04-2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LSG vs KKR</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LSG</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LSG</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>08:16:39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1442,6 +1442,33 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>26-04-2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GT vs CSK</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>08:16:45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -1433,12 +1433,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LSG</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08:16:39</t>
+          <t>08:16:54</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>CSK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>08:16:45</t>
+          <t>12:56:50</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LSG</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08:16:54</t>
+          <t>12:57:01</t>
         </is>
       </c>
     </row>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1469,6 +1469,33 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>27-04-2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DC vs RCB</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>14:59:12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1496,6 +1496,33 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>28-04-2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PBKS vs RR</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>09:58:19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1523,6 +1523,33 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>29-04-2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MI vs SRH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SRH</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>18:39:01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,6 +1550,33 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>30-04-2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>GT vs RCB</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>18:34:14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1577,6 +1577,33 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>01-05-2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RR vs DC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>18:47:11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1604,6 +1604,33 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>02-05-2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CSK vs MI</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>18:06:21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1631,6 +1631,33 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>03-05-2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SRH vs KKR</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SRH</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SRH</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>13:52:45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,6 +1658,33 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>03-05-2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GT vs PBKS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>13:52:54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1685,6 +1685,33 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MI vs LSG</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>15:51:33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1712,6 +1712,33 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>05-05-2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>DC vs CSK</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>18:28:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1739,6 +1739,33 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>06-05-2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SRH vs PBKS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SRH</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SRH</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>16:13:14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1766,6 +1766,33 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>08-05-2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>DC vs KKR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>18:31:43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1793,6 +1793,33 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>09-05-2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RR vs GT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>17:16:16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1820,6 +1820,33 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10-05-2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CSK vs LSG</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>14:36:42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1847,6 +1847,33 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10-05-2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>RCB vs MI</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>14:36:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1874,6 +1874,33 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>11-05-2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PBKS vs DC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>18:58:22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1901,6 +1901,33 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>13-05-2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RCB vs KKR</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>09:27:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1928,6 +1928,33 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>14-05-2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PBKS vs MI</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>18:30:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1955,6 +1955,33 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>15-05-2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LSG vs CSK</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>LSG</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LSG</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>18:53:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1982,6 +1982,33 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>16-05-2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KKR vs GT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>10:56:18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2009,6 +2009,33 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>17-05-2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PBKS vs RCB</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>14:00:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2036,6 +2036,33 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>17-05-2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>DC vs RR</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>14:00:59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2063,6 +2063,33 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>18-05-2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CSK vs SRH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>13:03:01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2090,6 +2090,33 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>19-05-2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>RR vs LSG</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>18:52:14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2117,6 +2117,33 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20-05-2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>KKR vs MI</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>18:31:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2144,6 +2144,33 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>21-05-2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CSK vs GT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CSK</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>18:41:11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2171,6 +2171,33 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>22-05-2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SRH vs RCB</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>18:30:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2198,6 +2198,33 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>23-05-2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LSG vs PBKS</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>LSG</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PBKS</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>14:31:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,6 +2225,33 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>24-05-2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>KKR vs DC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>15:03:21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2252,6 +2252,33 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>26-05-2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RCB vs GT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>16:39:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,33 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SRH vs RR</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SRH</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>17:19:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2306,6 +2306,33 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>29-05-2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>GT vs RR</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>18:30:51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/predictions_ajay.xlsx
+++ b/predictions_ajay.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2333,6 +2333,33 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>31-05-2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>RCB vs GT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>17:45:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
